--- a/config/union/union_skill.xlsx
+++ b/config/union/union_skill.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>生命の源</t>
+          <t>生命之源</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>物攻学習</t>
+          <t>物攻学习</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>特攻学習</t>
+          <t>特攻学习</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>物防強化</t>
+          <t>物防强化</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>特防強化</t>
+          <t>加强特防</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>強化訓練</t>
+          <t>强化训练</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>筋力鍛錬</t>
+          <t>肌肉锻炼</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>意志鍛錬</t>
+          <t>意志锻炼</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>肉体強化</t>
+          <t>身体强化</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>抵抗訓練</t>
+          <t>抵抗训练</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>抵抗強化</t>
+          <t>阻力增强</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>治療強化</t>
+          <t>治疗强化</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>会心強化</t>
+          <t>会心强化</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>会心ダメ強化</t>
+          <t>会心不行强化</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>会心耐性強化</t>
+          <t>暴击抵抗强化</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
